--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -875,7 +875,7 @@
     <t>コードは http://playbook.radlex.org/playbook/SearchRadlexAction に該当があれば使わなければならない。ただし、実施された行為のタイプにこれらのコードがなじまない場合は他のコードが利用される可能性がある。</t>
   </si>
   <si>
-    <t>http://playbook.radlex.org/playbook/SearchRadlexAction</t>
+    <t>http://www.rsna.org/RadLex_Playbook.aspx</t>
   </si>
   <si>
     <t>Event.code</t>
